--- a/report ready/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
+++ b/report ready/learner_phase5_integrated_phase4A_4D_results_FINAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangpinyi\Desktop\Lastinger\assessment-feedback-analysis\report ready\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3D9B7C-71AF-4AC8-985C-FE778253F61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8D14A9-7E23-4F46-B39B-F2A11CF8DAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -1311,7 +1311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1344,9 +1344,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1384,7 +1381,7 @@
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9601200" cy="5852160"/>
+    <xdr:ext cx="9601200" cy="5105399"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
@@ -1405,44 +1402,9 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="10620374" cy="5852160"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="5219700"/>
-          <a:ext cx="10620374" cy="5852160"/>
+          <a:off x="0" y="619125"/>
+          <a:ext cx="9601200" cy="5105399"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1473,7 +1435,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1512,7 +1474,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1529,6 +1491,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0611D4D-A56A-A824-2F61-5FEB1AB1441E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5962650"/>
+          <a:ext cx="8248650" cy="5095875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2212,7 +2218,7 @@
       <c r="C12" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="10">
         <v>0.98099999999999998</v>
       </c>
       <c r="F12" s="10" t="s">
@@ -3054,20 +3060,20 @@
   <dimension ref="A1:I67"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" style="14" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" style="14" customWidth="1"/>
-    <col min="4" max="11" width="22.7109375" style="14" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="14"/>
+    <col min="1" max="1" width="46.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="13" customWidth="1"/>
+    <col min="4" max="11" width="22.7109375" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3138,7 +3144,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>194</v>
       </c>
     </row>
@@ -3201,7 +3207,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="14" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3351,7 +3357,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="14" t="s">
         <v>225</v>
       </c>
     </row>
@@ -3436,7 +3442,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3905,7 +3911,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="14" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4048,20 +4054,20 @@
   <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.7109375" style="14" customWidth="1"/>
-    <col min="2" max="2" width="50" style="14" customWidth="1"/>
-    <col min="3" max="3" width="36.42578125" style="14" customWidth="1"/>
-    <col min="4" max="11" width="22.7109375" style="14" customWidth="1"/>
-    <col min="12" max="16384" width="11.42578125" style="14"/>
+    <col min="1" max="1" width="44.7109375" style="13" customWidth="1"/>
+    <col min="2" max="2" width="50" style="13" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" style="13" customWidth="1"/>
+    <col min="4" max="11" width="22.7109375" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4132,7 +4138,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4203,7 +4209,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4278,7 +4284,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="14" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4352,7 +4358,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="14" t="s">
         <v>286</v>
       </c>
     </row>
@@ -4549,7 +4555,7 @@
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="14" t="s">
         <v>297</v>
       </c>
     </row>
@@ -4608,7 +4614,7 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="14" t="s">
         <v>302</v>
       </c>
     </row>
